--- a/src/test/resources/testdata/Login.xlsx
+++ b/src/test/resources/testdata/Login.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phuongvt26\Selenium112023POMParallel\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A763305-CEB8-49A9-9C7D-E0D5FFC51A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047C8EA6-8220-40EA-9141-009AE9C689DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9060" activeTab="2" xr2:uid="{94D36197-2D82-4198-A459-BB3F4E5A65FC}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{94D36197-2D82-4198-A459-BB3F4E5A65FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
   <si>
     <t>TCS_NAME</t>
   </si>
@@ -78,15 +78,13 @@
   </si>
   <si>
     <t>Phuong1</t>
-  </si>
-  <si>
-    <t>123456</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -104,7 +102,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -113,6 +111,9 @@
     </fill>
     <fill>
       <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill/>
     </fill>
   </fills>
   <borders count="1">
@@ -128,16 +129,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -456,34 +478,34 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="17.21875" customWidth="1"/>
+    <col min="1" max="6" customWidth="true" width="17.21875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>10</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>123456</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -491,13 +513,13 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <v>10</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0">
         <v>1234567</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -505,13 +527,13 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0">
         <v>20</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="0">
         <v>12345678</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -533,25 +555,25 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="30.5546875" customWidth="1"/>
+    <col min="1" max="4" customWidth="true" width="30.5546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="7">
         <v>123456</v>
       </c>
     </row>
@@ -559,7 +581,7 @@
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="7">
         <v>123456</v>
       </c>
     </row>
@@ -567,14 +589,15 @@
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="7">
         <v>123456</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="C5" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -588,17 +611,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A10E1B-B69F-4FA2-AE27-D686BB01A2F2}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="30.5546875" customWidth="1"/>
+    <col min="1" max="3" customWidth="true" width="30.5546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>10</v>
       </c>
     </row>
@@ -606,33 +629,36 @@
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>14</v>
+      <c r="B2" s="2">
+        <v>123456</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>14</v>
+      <c r="B3" s="2">
+        <v>123456</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
+      <c r="B4" s="2">
+        <v>123456</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="B5" s="2">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
